--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_08-01-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_08-01-2026.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/25mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£9.70</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>£24.78</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/30mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£11.09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>£28.72</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/40mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£14.01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>£31.91</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>£37.78</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/60mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£18.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>N/L</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Error: 504 Server Error: Gateway Time-out for url: https://www.onlineinsulation-sales.com/product/70mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£20.24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>N/L</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/75mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£20.30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/80mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£23.38</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>£45.88</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/90mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£25.40</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>£53.74</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/100mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£25.00</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>£54.67</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/120mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£30.40</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>£64.44</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/140mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£37.79</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Error: 502 Server Error: Bad Gateway for url: https://www.onlineinsulation-sales.com/product/150mm-ecotherm-eco-versal-pir-insulation-board-2400x1200mm/</t>
+          <t>£37.32</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>£76.10</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
